--- a/docs/public/downloads/opening-final-checklist.xlsx
+++ b/docs/public/downloads/opening-final-checklist.xlsx
@@ -73,7 +73,7 @@
     <t>物件</t>
   </si>
   <si>
-    <t>上位店の最終承認済み</t>
+    <t>上位店のアドバイスを受けて最終選定済み</t>
   </si>
   <si>
     <t>賃貸借契約締結</t>
